--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N39_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N39_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>16.58617514866711</v>
       </c>
       <c r="E2" t="n">
-        <v>1.378052278638872</v>
+        <v>1.735502253879509</v>
       </c>
       <c r="F2" t="n">
-        <v>10.57819384691576</v>
+        <v>9.465860615838933</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -518,10 +518,10 @@
         <v>14.98381644334495</v>
       </c>
       <c r="E3" t="n">
-        <v>1.378052278638872</v>
+        <v>1.735502253879509</v>
       </c>
       <c r="F3" t="n">
-        <v>10.57819384691576</v>
+        <v>9.465860615838933</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>13.67114542178448</v>
+        <v>12.63156367335708</v>
       </c>
       <c r="D4" t="n">
-        <v>14.37281695811037</v>
+        <v>20.6793018752418</v>
       </c>
       <c r="E4" t="n">
-        <v>1.378052278638872</v>
+        <v>1.735502253879509</v>
       </c>
       <c r="F4" t="n">
-        <v>10.57819384691576</v>
+        <v>9.465860615838933</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,23 +576,55 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
+        <v>13.67114542178448</v>
+      </c>
+      <c r="D5" t="n">
+        <v>14.37281695811037</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.735502253879509</v>
+      </c>
+      <c r="F5" t="n">
+        <v>9.465860615838933</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>T6165</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>W0035F0003T0006Z000C1N39.png</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
         <v>17.29759034080104</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D6" t="n">
         <v>39.67214200621448</v>
       </c>
-      <c r="E5" t="n">
-        <v>1.378052278638872</v>
-      </c>
-      <c r="F5" t="n">
-        <v>10.57819384691576</v>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="E6" t="n">
+        <v>1.735502253879509</v>
+      </c>
+      <c r="F6" t="n">
+        <v>9.465860615838933</v>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>T6165</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N39_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N39_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>15.2327082492765</v>
+        <v>2.475315090507432</v>
       </c>
       <c r="D2" t="n">
-        <v>16.58617514866711</v>
+        <v>2.695253461658405</v>
       </c>
       <c r="E2" t="n">
-        <v>1.735502253879509</v>
+        <v>0.2820191162554203</v>
       </c>
       <c r="F2" t="n">
-        <v>9.465860615838933</v>
+        <v>1.538202350073827</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>16.54260756599448</v>
+        <v>2.688173729474102</v>
       </c>
       <c r="D3" t="n">
-        <v>14.98381644334495</v>
+        <v>2.434870172043555</v>
       </c>
       <c r="E3" t="n">
-        <v>1.735502253879509</v>
+        <v>0.2820191162554203</v>
       </c>
       <c r="F3" t="n">
-        <v>9.465860615838933</v>
+        <v>1.538202350073827</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>12.63156367335708</v>
+        <v>2.052629096920525</v>
       </c>
       <c r="D4" t="n">
-        <v>20.6793018752418</v>
+        <v>3.360386554726792</v>
       </c>
       <c r="E4" t="n">
-        <v>1.735502253879509</v>
+        <v>0.2820191162554203</v>
       </c>
       <c r="F4" t="n">
-        <v>9.465860615838933</v>
+        <v>1.538202350073827</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>13.67114542178448</v>
+        <v>2.221561131039977</v>
       </c>
       <c r="D5" t="n">
-        <v>14.37281695811037</v>
+        <v>2.335582755692935</v>
       </c>
       <c r="E5" t="n">
-        <v>1.735502253879509</v>
+        <v>0.2820191162554203</v>
       </c>
       <c r="F5" t="n">
-        <v>9.465860615838933</v>
+        <v>1.538202350073827</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.29759034080104</v>
+        <v>2.810858430380168</v>
       </c>
       <c r="D6" t="n">
-        <v>39.67214200621448</v>
+        <v>6.446723076009853</v>
       </c>
       <c r="E6" t="n">
-        <v>1.735502253879509</v>
+        <v>0.2820191162554203</v>
       </c>
       <c r="F6" t="n">
-        <v>9.465860615838933</v>
+        <v>1.538202350073827</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
